--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.443760893722313</v>
+        <v>1.209611145229876</v>
       </c>
       <c r="D2" t="n">
-        <v>7.603197634003055</v>
+        <v>1.235519615525497</v>
       </c>
       <c r="E2" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F2" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.00694376348044</v>
+        <v>4.388628361565571</v>
       </c>
       <c r="D3" t="n">
-        <v>25.00708625704407</v>
+        <v>4.063651516769662</v>
       </c>
       <c r="E3" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F3" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.06061311710691</v>
+        <v>1.959849631529872</v>
       </c>
       <c r="D4" t="n">
-        <v>78.89712652283484</v>
+        <v>12.82078305996066</v>
       </c>
       <c r="E4" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F4" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.0926211198836</v>
+        <v>4.565050931981085</v>
       </c>
       <c r="D5" t="n">
-        <v>94.90143355863783</v>
+        <v>15.42148295327865</v>
       </c>
       <c r="E5" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F5" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.91958343086674</v>
+        <v>7.624432307515845</v>
       </c>
       <c r="D6" t="n">
-        <v>25.35509996241995</v>
+        <v>4.120203743893242</v>
       </c>
       <c r="E6" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F6" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.17452347629371</v>
+        <v>4.903360064897729</v>
       </c>
       <c r="D7" t="n">
-        <v>77.8338123112698</v>
+        <v>12.64799450058134</v>
       </c>
       <c r="E7" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F7" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.64687444508322</v>
+        <v>2.380117097326023</v>
       </c>
       <c r="D8" t="n">
-        <v>16.37134378074377</v>
+        <v>2.660343364370863</v>
       </c>
       <c r="E8" t="n">
-        <v>12.49554747192789</v>
+        <v>2.030526464188283</v>
       </c>
       <c r="F8" t="n">
-        <v>33.17442697031123</v>
+        <v>5.390844382675575</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
